--- a/MATH/M08/bus123-math-m08-l01-follow-along.xlsx
+++ b/MATH/M08/bus123-math-m08-l01-follow-along.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="R727fd0bc5ad44572"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simple interest" sheetId="2" r:id="R34a27f118efb41cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note example" sheetId="3" r:id="Rb03f113616a2446b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="4" r:id="R0100739d395b4381"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Present value" sheetId="5" r:id="Rcf1cc3f1ca1c481f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenge" sheetId="6" r:id="Rf10094d5305d47d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START HERE" sheetId="1" r:id="Rca81e4f03a984037"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simple interest" sheetId="2" r:id="R511ec7a3c3e34633"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Note example" sheetId="3" r:id="R59373a42f61c47c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Live You Try It" sheetId="4" r:id="R34408bfd91444712"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Present value" sheetId="5" r:id="R0f706ad59d3c484f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenge" sheetId="6" r:id="R1af31a9348f74796"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -105,7 +105,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="32">
+  <x:cellXfs count="39">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -132,22 +132,45 @@
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="206" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="207" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="204" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="206" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="207" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="203" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="207" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="207" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -411,7 +434,7 @@
     <x:row r="6" ht="25" customHeight="1">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="6" t="str">
-        <x:v>Use alongside the PowerPoint</x:v>
+        <x:v>Use alongside the Canva deck</x:v>
       </x:c>
       <x:c r="C6" s="6"/>
       <x:c r="D6" s="6"/>
@@ -422,7 +445,7 @@
     <x:row r="7" ht="25" customHeight="1">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="4" t="str">
-        <x:v>Work through the tabs in slide order. Slide numbers appear above each example.</x:v>
+        <x:v>Use current Canva page positions (including the cover). Follow Simple interest, practice B, Note example, practice A, then Present value, practice C, and Challenge.</x:v>
       </x:c>
       <x:c r="C7" s="4"/>
       <x:c r="D7" s="4"/>
@@ -502,7 +525,7 @@
     <x:row r="15" ht="25" customHeight="1">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="4" t="str">
-        <x:v>Amounts, annual rates, and time inputs match the supplied PowerPoint. Keep full precision; currency displays cents.</x:v>
+        <x:v>Amounts, annual rates, and time inputs match the current Canva deck. Keep full precision; currency displays cents.</x:v>
       </x:c>
       <x:c r="C15" s="4"/>
       <x:c r="D15" s="4"/>
@@ -622,7 +645,7 @@
     <x:row r="27" ht="25" customHeight="1">
       <x:c r="A27" s="1"/>
       <x:c r="B27" s="4" t="str">
-        <x:v>BUS123 Math M08 Simple Interest.pptx • supplied 26-slide PowerPoint.</x:v>
+        <x:v>BUS123 Math M08 Canva deck • revised teaching sequence • 36 pages. The first eight pages are preserved.</x:v>
       </x:c>
       <x:c r="C27" s="4"/>
       <x:c r="D27" s="4"/>
@@ -1058,7 +1081,7 @@
     <x:row r="6" ht="25" customHeight="1">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="6" t="str">
-        <x:v>Slides 5–6 | Express time in years</x:v>
+        <x:v>Canva pages 6–7 | Express time in years</x:v>
       </x:c>
       <x:c r="C6" s="6"/>
       <x:c r="D6" s="6"/>
@@ -1097,7 +1120,7 @@
       <x:c r="B9" s="1" t="str">
         <x:v>Time in years</x:v>
       </x:c>
-      <x:c r="C9" s="26"/>
+      <x:c r="C9" s="32"/>
       <x:c r="D9" s="4" t="str">
         <x:v>Convert months to years.</x:v>
       </x:c>
@@ -1149,7 +1172,7 @@
       <x:c r="B13" s="1" t="str">
         <x:v>Exact time in years</x:v>
       </x:c>
-      <x:c r="C13" s="27"/>
+      <x:c r="C13" s="33"/>
       <x:c r="D13" s="1"/>
       <x:c r="E13" s="1"/>
       <x:c r="F13" s="1"/>
@@ -1160,7 +1183,7 @@
       <x:c r="B14" s="1" t="str">
         <x:v>Ordinary time in years</x:v>
       </x:c>
-      <x:c r="C14" s="27"/>
+      <x:c r="C14" s="33"/>
       <x:c r="D14" s="1"/>
       <x:c r="E14" s="1"/>
       <x:c r="F14" s="1"/>
@@ -1178,7 +1201,7 @@
     <x:row r="16" ht="25" customHeight="1">
       <x:c r="A16" s="1"/>
       <x:c r="B16" s="6" t="str">
-        <x:v>Slides 7, 10, 12–13 | Move money through time</x:v>
+        <x:v>Canva pages 8–15 | Move money through time</x:v>
       </x:c>
       <x:c r="C16" s="6"/>
       <x:c r="D16" s="6"/>
@@ -1230,7 +1253,7 @@
       <x:c r="B20" s="1" t="str">
         <x:v>Simple interest</x:v>
       </x:c>
-      <x:c r="C20" s="28"/>
+      <x:c r="C20" s="34"/>
       <x:c r="D20" s="4" t="str">
         <x:v>Principal × annual rate × years.</x:v>
       </x:c>
@@ -1243,7 +1266,7 @@
       <x:c r="B21" s="1" t="str">
         <x:v>Future value</x:v>
       </x:c>
-      <x:c r="C21" s="28"/>
+      <x:c r="C21" s="34"/>
       <x:c r="D21" s="4" t="str">
         <x:v>Include the original principal.</x:v>
       </x:c>
@@ -1256,7 +1279,7 @@
       <x:c r="B22" s="1" t="str">
         <x:v>Recover the principal</x:v>
       </x:c>
-      <x:c r="C22" s="28"/>
+      <x:c r="C22" s="34"/>
       <x:c r="D22" s="4" t="str">
         <x:v>Use interest, rate, and years.</x:v>
       </x:c>
@@ -1269,7 +1292,7 @@
       <x:c r="B23" s="1" t="str">
         <x:v>Discount future value to today</x:v>
       </x:c>
-      <x:c r="C23" s="28"/>
+      <x:c r="C23" s="34"/>
       <x:c r="D23" s="4" t="str">
         <x:v>Use the simple-interest growth factor.</x:v>
       </x:c>
@@ -1288,23 +1311,17 @@
     </x:row>
     <x:row r="25" ht="25" customHeight="1">
       <x:c r="A25" s="1"/>
-      <x:c r="B25" s="6" t="str">
-        <x:v>Slide 8 | Exact-interest note</x:v>
-      </x:c>
-      <x:c r="C25" s="6"/>
-      <x:c r="D25" s="6"/>
-      <x:c r="E25" s="6"/>
-      <x:c r="F25" s="6"/>
-      <x:c r="G25" s="6"/>
+      <x:c r="B25" s="1"/>
+      <x:c r="C25" s="1"/>
+      <x:c r="D25" s="1"/>
+      <x:c r="E25" s="1"/>
+      <x:c r="F25" s="1"/>
+      <x:c r="G25" s="1"/>
     </x:row>
     <x:row r="26" ht="25" customHeight="1">
       <x:c r="A26" s="1"/>
-      <x:c r="B26" s="1" t="str">
-        <x:v>Principal</x:v>
-      </x:c>
-      <x:c r="C26" s="12" t="n">
-        <x:v>32000</x:v>
-      </x:c>
+      <x:c r="B26" s="1"/>
+      <x:c r="C26" s="1"/>
       <x:c r="D26" s="1"/>
       <x:c r="E26" s="1"/>
       <x:c r="F26" s="1"/>
@@ -1312,12 +1329,8 @@
     </x:row>
     <x:row r="27" ht="25" customHeight="1">
       <x:c r="A27" s="1"/>
-      <x:c r="B27" s="1" t="str">
-        <x:v>Annual rate</x:v>
-      </x:c>
-      <x:c r="C27" s="13" t="n">
-        <x:v>0.045</x:v>
-      </x:c>
+      <x:c r="B27" s="1"/>
+      <x:c r="C27" s="1"/>
       <x:c r="D27" s="1"/>
       <x:c r="E27" s="1"/>
       <x:c r="F27" s="1"/>
@@ -1325,12 +1338,8 @@
     </x:row>
     <x:row r="28" ht="25" customHeight="1">
       <x:c r="A28" s="1"/>
-      <x:c r="B28" s="1" t="str">
-        <x:v>Exact days</x:v>
-      </x:c>
-      <x:c r="C28" s="7" t="n">
-        <x:v>80</x:v>
-      </x:c>
+      <x:c r="B28" s="1"/>
+      <x:c r="C28" s="1"/>
       <x:c r="D28" s="1"/>
       <x:c r="E28" s="1"/>
       <x:c r="F28" s="1"/>
@@ -1338,12 +1347,8 @@
     </x:row>
     <x:row r="29" ht="25" customHeight="1">
       <x:c r="A29" s="1"/>
-      <x:c r="B29" s="1" t="str">
-        <x:v>Days per year</x:v>
-      </x:c>
-      <x:c r="C29" s="7" t="n">
-        <x:v>365</x:v>
-      </x:c>
+      <x:c r="B29" s="1"/>
+      <x:c r="C29" s="1"/>
       <x:c r="D29" s="1"/>
       <x:c r="E29" s="1"/>
       <x:c r="F29" s="1"/>
@@ -1351,27 +1356,21 @@
     </x:row>
     <x:row r="30" ht="25" customHeight="1">
       <x:c r="A30" s="1"/>
-      <x:c r="B30" s="1" t="str">
-        <x:v>Time in years</x:v>
-      </x:c>
-      <x:c r="C30" s="27"/>
+      <x:c r="B30" s="1"/>
+      <x:c r="C30" s="1"/>
       <x:c r="D30" s="1"/>
       <x:c r="E30" s="1"/>
       <x:c r="F30" s="1"/>
       <x:c r="G30" s="1"/>
     </x:row>
-    <x:row r="31" ht="38" customHeight="1">
+    <x:row r="31" ht="25" customHeight="1">
       <x:c r="A31" s="1"/>
-      <x:c r="B31" s="1" t="str">
-        <x:v>Simple interest</x:v>
-      </x:c>
-      <x:c r="C31" s="28"/>
-      <x:c r="D31" s="4" t="str">
-        <x:v>Calculate using the year fraction.</x:v>
-      </x:c>
-      <x:c r="E31" s="4"/>
-      <x:c r="F31" s="4"/>
-      <x:c r="G31" s="4"/>
+      <x:c r="B31" s="1"/>
+      <x:c r="C31" s="1"/>
+      <x:c r="D31" s="1"/>
+      <x:c r="E31" s="1"/>
+      <x:c r="F31" s="1"/>
+      <x:c r="G31" s="1"/>
     </x:row>
     <x:row r="32" ht="25" customHeight="1">
       <x:c r="A32" s="1"/>
@@ -1690,8 +1689,6 @@
     <x:mergeCell ref="D21:G21"/>
     <x:mergeCell ref="D22:G22"/>
     <x:mergeCell ref="D23:G23"/>
-    <x:mergeCell ref="B25:G25"/>
-    <x:mergeCell ref="D31:G31"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1708,7 +1705,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="16" t="str">
-        <x:v>Slide 8 | Exact-interest note</x:v>
+        <x:v>Canva page 18 | Exact-interest note</x:v>
       </x:c>
       <x:c r="B1" s="16" t="str">
         <x:v>Value</x:v>
@@ -1725,7 +1722,7 @@
       </x:c>
       <x:c r="C2" s="16"/>
       <x:c r="D2" s="20" t="str">
-        <x:v>Enter your formula in B6 using B2:B5, as shown in slide 8.</x:v>
+        <x:v>Canva page 18: build B6 using B2:B5. Use this tab for the guided note example; then switch to Live You Try It for checkpoint A.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1803,12 +1800,12 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="3" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="39" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="20" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="3" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="31" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="23" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="23" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="23" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="23" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="25" customHeight="1">
@@ -1823,7 +1820,7 @@
     <x:row r="2" ht="36" customHeight="1">
       <x:c r="A2" s="1"/>
       <x:c r="B2" s="3" t="str">
-        <x:v>Live You Try It | Slides 9, 11, 17</x:v>
+        <x:v>Live You Try It | Checkpoints B → A → C</x:v>
       </x:c>
       <x:c r="C2" s="3"/>
       <x:c r="D2" s="3"/>
@@ -1834,7 +1831,7 @@
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1"/>
       <x:c r="B3" s="4" t="str">
-        <x:v>Build the yellow cells using references. Optional transfer uses its own inputs.</x:v>
+        <x:v>Use cell references. B: pages 16–17; A: pages 19–20; C: pages 25–26. Record a short explanation below each prompt.</x:v>
       </x:c>
       <x:c r="C3" s="4"/>
       <x:c r="D3" s="4"/>
@@ -1851,213 +1848,215 @@
       <x:c r="F4" s="4"/>
       <x:c r="G4" s="4"/>
     </x:row>
-    <x:row r="5" ht="25" customHeight="1">
+    <x:row r="5" ht="42" customHeight="1">
       <x:c r="A5" s="1"/>
       <x:c r="B5" s="1"/>
-      <x:c r="C5" s="1" t="str">
-        <x:v>Task</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="str">
-        <x:v>Input 1</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="str">
-        <x:v>Input 2</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="str">
-        <x:v>Input 3</x:v>
-      </x:c>
-      <x:c r="G5" s="1" t="str">
-        <x:v>Build here</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="25" customHeight="1">
+      <x:c r="C5" s="27" t="str">
+        <x:v>Calculation</x:v>
+      </x:c>
+      <x:c r="D5" s="27" t="str">
+        <x:v>Days / amount</x:v>
+      </x:c>
+      <x:c r="E5" s="27" t="str">
+        <x:v>Year basis / rate</x:v>
+      </x:c>
+      <x:c r="F5" s="27" t="str">
+        <x:v>Years / linked value</x:v>
+      </x:c>
+      <x:c r="G5" s="27" t="str">
+        <x:v>Your result</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="32" customHeight="1">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="1"/>
-      <x:c r="C6" s="1" t="str">
+      <x:c r="C6" s="4" t="str">
         <x:v>A1 Exact time</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="n">
+      <x:c r="D6" s="4" t="n">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="E6" s="1" t="n">
+      <x:c r="E6" s="4" t="n">
         <x:v>365</x:v>
       </x:c>
-      <x:c r="F6" s="1"/>
-      <x:c r="G6" s="27"/>
-    </x:row>
-    <x:row r="7" ht="25" customHeight="1">
+      <x:c r="F6" s="4"/>
+      <x:c r="G6" s="35"/>
+    </x:row>
+    <x:row r="7" ht="32" customHeight="1">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1"/>
-      <x:c r="C7" s="1" t="str">
+      <x:c r="C7" s="4" t="str">
         <x:v>A2 Exact interest</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="n">
+      <x:c r="D7" s="25" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="E7" s="13" t="n">
+      <x:c r="E7" s="23" t="n">
         <x:v>0.048</x:v>
       </x:c>
-      <x:c r="F7" s="1" t="str">
+      <x:c r="F7" s="4" t="str">
         <x:f>IF(G6="","",G6)</x:f>
       </x:c>
-      <x:c r="G7" s="28"/>
-    </x:row>
-    <x:row r="8" ht="25" customHeight="1">
+      <x:c r="G7" s="36"/>
+    </x:row>
+    <x:row r="8" ht="32" customHeight="1">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1"/>
-      <x:c r="C8" s="1" t="str">
+      <x:c r="C8" s="4" t="str">
         <x:v>A3 Ordinary time</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="n">
+      <x:c r="D8" s="4" t="n">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="E8" s="1" t="n">
+      <x:c r="E8" s="4" t="n">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="F8" s="1"/>
-      <x:c r="G8" s="27"/>
-    </x:row>
-    <x:row r="9" ht="25" customHeight="1">
+      <x:c r="F8" s="4"/>
+      <x:c r="G8" s="35"/>
+    </x:row>
+    <x:row r="9" ht="32" customHeight="1">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="1"/>
-      <x:c r="C9" s="1" t="str">
+      <x:c r="C9" s="4" t="str">
         <x:v>A4 Ordinary interest</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="n">
+      <x:c r="D9" s="25" t="n">
         <x:v>42000</x:v>
       </x:c>
-      <x:c r="E9" s="13" t="n">
+      <x:c r="E9" s="23" t="n">
         <x:v>0.048</x:v>
       </x:c>
-      <x:c r="F9" s="29"/>
-      <x:c r="G9" s="28"/>
-    </x:row>
-    <x:row r="10" ht="25" customHeight="1">
+      <x:c r="F9" s="4" t="str">
+        <x:f>IF(G8="","",G8)</x:f>
+      </x:c>
+      <x:c r="G9" s="36"/>
+    </x:row>
+    <x:row r="10" ht="32" customHeight="1">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1"/>
-      <x:c r="C10" s="1" t="str">
+      <x:c r="C10" s="4" t="str">
         <x:v>A5 Ordinary − exact</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="str">
+      <x:c r="D10" s="25" t="str">
         <x:f>IF(G7="","",G7)</x:f>
       </x:c>
-      <x:c r="E10" s="1" t="str">
+      <x:c r="E10" s="25" t="str">
         <x:f>IF(G9="","",G9)</x:f>
       </x:c>
-      <x:c r="F10" s="1"/>
-      <x:c r="G10" s="28"/>
-    </x:row>
-    <x:row r="11" ht="25" customHeight="1">
+      <x:c r="F10" s="4"/>
+      <x:c r="G10" s="36"/>
+    </x:row>
+    <x:row r="11" ht="32" customHeight="1">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1"/>
-      <x:c r="C11" s="1"/>
-      <x:c r="D11" s="1"/>
-      <x:c r="E11" s="1"/>
-      <x:c r="F11" s="1"/>
-      <x:c r="G11" s="12"/>
-    </x:row>
-    <x:row r="12" ht="25" customHeight="1">
+      <x:c r="C11" s="4"/>
+      <x:c r="D11" s="4"/>
+      <x:c r="E11" s="4"/>
+      <x:c r="F11" s="4"/>
+      <x:c r="G11" s="25"/>
+    </x:row>
+    <x:row r="12" ht="32" customHeight="1">
       <x:c r="A12" s="1"/>
       <x:c r="B12" s="1"/>
-      <x:c r="C12" s="1" t="str">
+      <x:c r="C12" s="4" t="str">
         <x:v>B1 Years</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="n">
+      <x:c r="D12" s="4" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="n">
+      <x:c r="E12" s="4" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="F12" s="1"/>
-      <x:c r="G12" s="27"/>
-    </x:row>
-    <x:row r="13" ht="25" customHeight="1">
+      <x:c r="F12" s="4"/>
+      <x:c r="G12" s="35"/>
+    </x:row>
+    <x:row r="13" ht="32" customHeight="1">
       <x:c r="A13" s="1"/>
       <x:c r="B13" s="1"/>
-      <x:c r="C13" s="1" t="str">
+      <x:c r="C13" s="4" t="str">
         <x:v>B2 Interest</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="n">
+      <x:c r="D13" s="25" t="n">
         <x:v>18500</x:v>
       </x:c>
-      <x:c r="E13" s="13" t="n">
+      <x:c r="E13" s="23" t="n">
         <x:v>0.062</x:v>
       </x:c>
-      <x:c r="F13" s="1" t="str">
+      <x:c r="F13" s="4" t="str">
         <x:f>IF(G12="","",G12)</x:f>
       </x:c>
-      <x:c r="G13" s="28"/>
-    </x:row>
-    <x:row r="14" ht="25" customHeight="1">
+      <x:c r="G13" s="36"/>
+    </x:row>
+    <x:row r="14" ht="32" customHeight="1">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1"/>
-      <x:c r="C14" s="1" t="str">
+      <x:c r="C14" s="4" t="str">
         <x:v>B3 Future value</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="n">
+      <x:c r="D14" s="25" t="n">
         <x:v>18500</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="str">
+      <x:c r="E14" s="25" t="str">
         <x:f>IF(G13="","",G13)</x:f>
       </x:c>
-      <x:c r="F14" s="1"/>
-      <x:c r="G14" s="28"/>
-    </x:row>
-    <x:row r="15" ht="25" customHeight="1">
+      <x:c r="F14" s="4"/>
+      <x:c r="G14" s="36"/>
+    </x:row>
+    <x:row r="15" ht="32" customHeight="1">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1"/>
-      <x:c r="C15" s="1"/>
-      <x:c r="D15" s="1"/>
-      <x:c r="E15" s="1"/>
-      <x:c r="F15" s="1"/>
-      <x:c r="G15" s="12"/>
-    </x:row>
-    <x:row r="16" ht="25" customHeight="1">
+      <x:c r="C15" s="4"/>
+      <x:c r="D15" s="4"/>
+      <x:c r="E15" s="4"/>
+      <x:c r="F15" s="4"/>
+      <x:c r="G15" s="25"/>
+    </x:row>
+    <x:row r="16" ht="32" customHeight="1">
       <x:c r="A16" s="1"/>
       <x:c r="B16" s="1"/>
-      <x:c r="C16" s="1" t="str">
+      <x:c r="C16" s="4" t="str">
         <x:v>C1 PV outflow</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="n">
+      <x:c r="D16" s="25" t="n">
         <x:v>30000</x:v>
       </x:c>
-      <x:c r="E16" s="13" t="n">
+      <x:c r="E16" s="23" t="n">
         <x:v>0.065</x:v>
       </x:c>
-      <x:c r="F16" s="1" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="G16" s="28"/>
-    </x:row>
-    <x:row r="17" ht="25" customHeight="1">
+      <x:c r="F16" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G16" s="36"/>
+    </x:row>
+    <x:row r="17" ht="32" customHeight="1">
       <x:c r="A17" s="1"/>
       <x:c r="B17" s="1"/>
-      <x:c r="C17" s="1" t="str">
+      <x:c r="C17" s="4" t="str">
         <x:v>C2 Positive PV</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="str">
+      <x:c r="D17" s="25" t="str">
         <x:f>IF(G16="","",G16)</x:f>
       </x:c>
-      <x:c r="E17" s="1"/>
-      <x:c r="F17" s="1"/>
-      <x:c r="G17" s="28"/>
-    </x:row>
-    <x:row r="18" ht="25" customHeight="1">
+      <x:c r="E17" s="4"/>
+      <x:c r="F17" s="4"/>
+      <x:c r="G17" s="36"/>
+    </x:row>
+    <x:row r="18" ht="32" customHeight="1">
       <x:c r="A18" s="1"/>
       <x:c r="B18" s="1"/>
-      <x:c r="C18" s="1" t="str">
+      <x:c r="C18" s="4" t="str">
         <x:v>C3 FV check</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="str">
+      <x:c r="D18" s="25" t="str">
         <x:f>IF(G16="","",G16)</x:f>
       </x:c>
-      <x:c r="E18" s="13" t="n">
+      <x:c r="E18" s="23" t="n">
         <x:v>0.065</x:v>
       </x:c>
-      <x:c r="F18" s="1" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="G18" s="28"/>
+      <x:c r="F18" s="4" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G18" s="36"/>
     </x:row>
     <x:row r="19" ht="25" customHeight="1">
       <x:c r="A19" s="1"/>
@@ -2077,10 +2076,10 @@
       <x:c r="F20" s="1"/>
       <x:c r="G20" s="1"/>
     </x:row>
-    <x:row r="21" ht="25" customHeight="1">
+    <x:row r="21" ht="33" customHeight="1">
       <x:c r="A21" s="1"/>
       <x:c r="B21" s="4" t="str">
-        <x:v>A: Link F9 to G8; compare ordinary interest with exact interest. B: Calculate time, interest, then total balance. C (optional): Find signed PV, show its positive magnitude, then verify with FV.</x:v>
+        <x:v>Complete each checkpoint when prompted in Canva. B: Meridian borrows $18,500 for 8 months at 6.2% simple interest. A: compare 75-day interest on $42,000 at 4.8%. C: value a $30,000 receipt in 2 years at 6.5% annual compound discounting.</x:v>
       </x:c>
       <x:c r="C21" s="4"/>
       <x:c r="D21" s="4"/>
@@ -2088,7 +2087,7 @@
       <x:c r="F21" s="4"/>
       <x:c r="G21" s="4"/>
     </x:row>
-    <x:row r="22" ht="25" customHeight="1">
+    <x:row r="22" ht="33" customHeight="1">
       <x:c r="A22" s="1"/>
       <x:c r="B22" s="4"/>
       <x:c r="C22" s="4"/>
@@ -2097,7 +2096,7 @@
       <x:c r="F22" s="4"/>
       <x:c r="G22" s="4"/>
     </x:row>
-    <x:row r="23" ht="25" customHeight="1">
+    <x:row r="23" ht="33" customHeight="1">
       <x:c r="A23" s="1"/>
       <x:c r="B23" s="4"/>
       <x:c r="C23" s="4"/>
@@ -2115,41 +2114,43 @@
       <x:c r="F24" s="1"/>
       <x:c r="G24" s="1"/>
     </x:row>
-    <x:row r="25" ht="25" customHeight="1">
+    <x:row r="25" ht="38" customHeight="1">
       <x:c r="A25" s="1"/>
-      <x:c r="B25" s="1"/>
-      <x:c r="C25" s="1"/>
-      <x:c r="D25" s="1"/>
-      <x:c r="E25" s="1"/>
-      <x:c r="F25" s="1"/>
-      <x:c r="G25" s="1"/>
-    </x:row>
-    <x:row r="26" ht="25" customHeight="1">
+      <x:c r="B25" s="27" t="str">
+        <x:v>A | Why does the ordinary basis produce more interest? D10 = exact; E10 = ordinary.</x:v>
+      </x:c>
+      <x:c r="C25" s="27"/>
+      <x:c r="D25" s="27"/>
+      <x:c r="E25" s="27"/>
+      <x:c r="F25" s="27"/>
+      <x:c r="G25" s="27"/>
+    </x:row>
+    <x:row r="26" ht="28" customHeight="1">
       <x:c r="A26" s="1"/>
-      <x:c r="B26" s="1"/>
-      <x:c r="C26" s="1"/>
-      <x:c r="D26" s="1"/>
-      <x:c r="E26" s="1"/>
-      <x:c r="F26" s="1"/>
-      <x:c r="G26" s="1"/>
-    </x:row>
-    <x:row r="27" ht="25" customHeight="1">
+      <x:c r="B26" s="37"/>
+      <x:c r="C26" s="29"/>
+      <x:c r="D26" s="29"/>
+      <x:c r="E26" s="29"/>
+      <x:c r="F26" s="29"/>
+      <x:c r="G26" s="29"/>
+    </x:row>
+    <x:row r="27" ht="28" customHeight="1">
       <x:c r="A27" s="1"/>
-      <x:c r="B27" s="1"/>
-      <x:c r="C27" s="1"/>
-      <x:c r="D27" s="1"/>
-      <x:c r="E27" s="1"/>
-      <x:c r="F27" s="1"/>
-      <x:c r="G27" s="1"/>
-    </x:row>
-    <x:row r="28" ht="25" customHeight="1">
+      <x:c r="B27" s="29"/>
+      <x:c r="C27" s="29"/>
+      <x:c r="D27" s="29"/>
+      <x:c r="E27" s="29"/>
+      <x:c r="F27" s="29"/>
+      <x:c r="G27" s="29"/>
+    </x:row>
+    <x:row r="28" ht="28" customHeight="1">
       <x:c r="A28" s="1"/>
-      <x:c r="B28" s="1"/>
-      <x:c r="C28" s="1"/>
-      <x:c r="D28" s="1"/>
-      <x:c r="E28" s="1"/>
-      <x:c r="F28" s="1"/>
-      <x:c r="G28" s="1"/>
+      <x:c r="B28" s="29"/>
+      <x:c r="C28" s="29"/>
+      <x:c r="D28" s="29"/>
+      <x:c r="E28" s="29"/>
+      <x:c r="F28" s="29"/>
+      <x:c r="G28" s="29"/>
     </x:row>
     <x:row r="29" ht="25" customHeight="1">
       <x:c r="A29" s="1"/>
@@ -2160,41 +2161,43 @@
       <x:c r="F29" s="1"/>
       <x:c r="G29" s="1"/>
     </x:row>
-    <x:row r="30" ht="25" customHeight="1">
+    <x:row r="30" ht="38" customHeight="1">
       <x:c r="A30" s="1"/>
-      <x:c r="B30" s="1"/>
-      <x:c r="C30" s="1"/>
-      <x:c r="D30" s="1"/>
-      <x:c r="E30" s="1"/>
-      <x:c r="F30" s="1"/>
-      <x:c r="G30" s="1"/>
-    </x:row>
-    <x:row r="31" ht="25" customHeight="1">
+      <x:c r="B30" s="27" t="str">
+        <x:v>B | How much of the repayment is interest, and how much is principal?</x:v>
+      </x:c>
+      <x:c r="C30" s="27"/>
+      <x:c r="D30" s="27"/>
+      <x:c r="E30" s="27"/>
+      <x:c r="F30" s="27"/>
+      <x:c r="G30" s="27"/>
+    </x:row>
+    <x:row r="31" ht="28" customHeight="1">
       <x:c r="A31" s="1"/>
-      <x:c r="B31" s="1"/>
-      <x:c r="C31" s="1"/>
-      <x:c r="D31" s="1"/>
-      <x:c r="E31" s="1"/>
-      <x:c r="F31" s="1"/>
-      <x:c r="G31" s="1"/>
-    </x:row>
-    <x:row r="32" ht="25" customHeight="1">
+      <x:c r="B31" s="37"/>
+      <x:c r="C31" s="29"/>
+      <x:c r="D31" s="29"/>
+      <x:c r="E31" s="29"/>
+      <x:c r="F31" s="29"/>
+      <x:c r="G31" s="29"/>
+    </x:row>
+    <x:row r="32" ht="28" customHeight="1">
       <x:c r="A32" s="1"/>
-      <x:c r="B32" s="1"/>
-      <x:c r="C32" s="1"/>
-      <x:c r="D32" s="1"/>
-      <x:c r="E32" s="1"/>
-      <x:c r="F32" s="1"/>
-      <x:c r="G32" s="1"/>
-    </x:row>
-    <x:row r="33" ht="25" customHeight="1">
+      <x:c r="B32" s="29"/>
+      <x:c r="C32" s="29"/>
+      <x:c r="D32" s="29"/>
+      <x:c r="E32" s="29"/>
+      <x:c r="F32" s="29"/>
+      <x:c r="G32" s="29"/>
+    </x:row>
+    <x:row r="33" ht="28" customHeight="1">
       <x:c r="A33" s="1"/>
-      <x:c r="B33" s="1"/>
-      <x:c r="C33" s="1"/>
-      <x:c r="D33" s="1"/>
-      <x:c r="E33" s="1"/>
-      <x:c r="F33" s="1"/>
-      <x:c r="G33" s="1"/>
+      <x:c r="B33" s="29"/>
+      <x:c r="C33" s="29"/>
+      <x:c r="D33" s="29"/>
+      <x:c r="E33" s="29"/>
+      <x:c r="F33" s="29"/>
+      <x:c r="G33" s="29"/>
     </x:row>
     <x:row r="34" ht="25" customHeight="1">
       <x:c r="A34" s="1"/>
@@ -2205,41 +2208,43 @@
       <x:c r="F34" s="1"/>
       <x:c r="G34" s="1"/>
     </x:row>
-    <x:row r="35" ht="25" customHeight="1">
+    <x:row r="35" ht="38" customHeight="1">
       <x:c r="A35" s="1"/>
-      <x:c r="B35" s="1"/>
-      <x:c r="C35" s="1"/>
-      <x:c r="D35" s="1"/>
-      <x:c r="E35" s="1"/>
-      <x:c r="F35" s="1"/>
-      <x:c r="G35" s="1"/>
-    </x:row>
-    <x:row r="36" ht="25" customHeight="1">
+      <x:c r="B35" s="27" t="str">
+        <x:v>C | Explain the negative PV and what the FV check confirms.</x:v>
+      </x:c>
+      <x:c r="C35" s="27"/>
+      <x:c r="D35" s="27"/>
+      <x:c r="E35" s="27"/>
+      <x:c r="F35" s="27"/>
+      <x:c r="G35" s="27"/>
+    </x:row>
+    <x:row r="36" ht="28" customHeight="1">
       <x:c r="A36" s="1"/>
-      <x:c r="B36" s="1"/>
-      <x:c r="C36" s="1"/>
-      <x:c r="D36" s="1"/>
-      <x:c r="E36" s="1"/>
-      <x:c r="F36" s="1"/>
-      <x:c r="G36" s="1"/>
-    </x:row>
-    <x:row r="37" ht="25" customHeight="1">
+      <x:c r="B36" s="37"/>
+      <x:c r="C36" s="29"/>
+      <x:c r="D36" s="29"/>
+      <x:c r="E36" s="29"/>
+      <x:c r="F36" s="29"/>
+      <x:c r="G36" s="29"/>
+    </x:row>
+    <x:row r="37" ht="28" customHeight="1">
       <x:c r="A37" s="1"/>
-      <x:c r="B37" s="1"/>
-      <x:c r="C37" s="1"/>
-      <x:c r="D37" s="1"/>
-      <x:c r="E37" s="1"/>
-      <x:c r="F37" s="1"/>
-      <x:c r="G37" s="1"/>
-    </x:row>
-    <x:row r="38" ht="25" customHeight="1">
+      <x:c r="B37" s="29"/>
+      <x:c r="C37" s="29"/>
+      <x:c r="D37" s="29"/>
+      <x:c r="E37" s="29"/>
+      <x:c r="F37" s="29"/>
+      <x:c r="G37" s="29"/>
+    </x:row>
+    <x:row r="38" ht="28" customHeight="1">
       <x:c r="A38" s="1"/>
-      <x:c r="B38" s="1"/>
-      <x:c r="C38" s="1"/>
-      <x:c r="D38" s="1"/>
-      <x:c r="E38" s="1"/>
-      <x:c r="F38" s="1"/>
-      <x:c r="G38" s="1"/>
+      <x:c r="B38" s="29"/>
+      <x:c r="C38" s="29"/>
+      <x:c r="D38" s="29"/>
+      <x:c r="E38" s="29"/>
+      <x:c r="F38" s="29"/>
+      <x:c r="G38" s="29"/>
     </x:row>
     <x:row r="39" ht="25" customHeight="1">
       <x:c r="A39" s="1"/>
@@ -2489,6 +2494,12 @@
     <x:mergeCell ref="B2:G2"/>
     <x:mergeCell ref="B3:G4"/>
     <x:mergeCell ref="B21:G23"/>
+    <x:mergeCell ref="B25:G25"/>
+    <x:mergeCell ref="B26:G28"/>
+    <x:mergeCell ref="B30:G30"/>
+    <x:mergeCell ref="B31:G33"/>
+    <x:mergeCell ref="B35:G35"/>
+    <x:mergeCell ref="B36:G38"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2559,7 +2570,7 @@
     <x:row r="6" ht="25" customHeight="1">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="6" t="str">
-        <x:v>Slides 14–16 | Two years, two growth models</x:v>
+        <x:v>Canva pages 21–24 | Two-year models and Excel</x:v>
       </x:c>
       <x:c r="C6" s="6"/>
       <x:c r="D6" s="6"/>
@@ -2611,7 +2622,7 @@
       <x:c r="B10" s="1" t="str">
         <x:v>Simple future value</x:v>
       </x:c>
-      <x:c r="C10" s="28"/>
+      <x:c r="C10" s="34"/>
       <x:c r="D10" s="1"/>
       <x:c r="E10" s="1"/>
       <x:c r="F10" s="1"/>
@@ -2622,7 +2633,7 @@
       <x:c r="B11" s="1" t="str">
         <x:v>Compound future value</x:v>
       </x:c>
-      <x:c r="C11" s="28"/>
+      <x:c r="C11" s="34"/>
       <x:c r="D11" s="1"/>
       <x:c r="E11" s="1"/>
       <x:c r="F11" s="1"/>
@@ -2646,7 +2657,7 @@
       <x:c r="B13" s="1" t="str">
         <x:v>Simple present value</x:v>
       </x:c>
-      <x:c r="C13" s="28"/>
+      <x:c r="C13" s="34"/>
       <x:c r="D13" s="1"/>
       <x:c r="E13" s="1"/>
       <x:c r="F13" s="1"/>
@@ -2657,7 +2668,7 @@
       <x:c r="B14" s="1" t="str">
         <x:v>Compound present value (+)</x:v>
       </x:c>
-      <x:c r="C14" s="28"/>
+      <x:c r="C14" s="34"/>
       <x:c r="D14" s="4" t="str">
         <x:v>Display a positive value today.</x:v>
       </x:c>
@@ -2670,7 +2681,7 @@
       <x:c r="B15" s="1" t="str">
         <x:v>PV cash outflow (−)</x:v>
       </x:c>
-      <x:c r="C15" s="28"/>
+      <x:c r="C15" s="34"/>
       <x:c r="D15" s="4" t="str">
         <x:v>Use the investor cash-flow direction.</x:v>
       </x:c>
@@ -2683,7 +2694,7 @@
       <x:c r="B16" s="1" t="str">
         <x:v>FV verification</x:v>
       </x:c>
-      <x:c r="C16" s="28"/>
+      <x:c r="C16" s="34"/>
       <x:c r="D16" s="4" t="str">
         <x:v>Grow the negative present outflow forward.</x:v>
       </x:c>
@@ -2703,7 +2714,7 @@
     <x:row r="18" ht="25" customHeight="1">
       <x:c r="A18" s="1"/>
       <x:c r="B18" s="6" t="str">
-        <x:v>Slide 17 | A wait in months</x:v>
+        <x:v>Canva page 27 | Fractional-year extension</x:v>
       </x:c>
       <x:c r="C18" s="6"/>
       <x:c r="D18" s="6"/>
@@ -2768,7 +2779,7 @@
       <x:c r="B23" s="1" t="str">
         <x:v>Annual periods</x:v>
       </x:c>
-      <x:c r="C23" s="26"/>
+      <x:c r="C23" s="32"/>
       <x:c r="D23" s="1"/>
       <x:c r="E23" s="1"/>
       <x:c r="F23" s="1"/>
@@ -2779,7 +2790,7 @@
       <x:c r="B24" s="1" t="str">
         <x:v>Positive compound PV</x:v>
       </x:c>
-      <x:c r="C24" s="28"/>
+      <x:c r="C24" s="34"/>
       <x:c r="D24" s="1"/>
       <x:c r="E24" s="1"/>
       <x:c r="F24" s="1"/>
@@ -2797,7 +2808,7 @@
     <x:row r="26" ht="25" customHeight="1">
       <x:c r="A26" s="1"/>
       <x:c r="B26" s="6" t="str">
-        <x:v>Slides 18–20 | Time and rate sensitivity</x:v>
+        <x:v>Canva pages 28–30 | Time and rate sensitivity</x:v>
       </x:c>
       <x:c r="C26" s="6"/>
       <x:c r="D26" s="6"/>
@@ -2846,34 +2857,34 @@
     </x:row>
     <x:row r="30" ht="25" customHeight="1">
       <x:c r="A30" s="1"/>
-      <x:c r="B30" s="22" t="n">
+      <x:c r="B30" s="30" t="n">
         <x:v>0.04</x:v>
       </x:c>
-      <x:c r="C30" s="30"/>
-      <x:c r="D30" s="30"/>
-      <x:c r="E30" s="30"/>
+      <x:c r="C30" s="38"/>
+      <x:c r="D30" s="38"/>
+      <x:c r="E30" s="38"/>
       <x:c r="F30" s="1"/>
       <x:c r="G30" s="1"/>
     </x:row>
     <x:row r="31" ht="25" customHeight="1">
       <x:c r="A31" s="1"/>
-      <x:c r="B31" s="22" t="n">
+      <x:c r="B31" s="30" t="n">
         <x:v>0.06</x:v>
       </x:c>
-      <x:c r="C31" s="30"/>
-      <x:c r="D31" s="30"/>
-      <x:c r="E31" s="30"/>
+      <x:c r="C31" s="38"/>
+      <x:c r="D31" s="38"/>
+      <x:c r="E31" s="38"/>
       <x:c r="F31" s="1"/>
       <x:c r="G31" s="1"/>
     </x:row>
     <x:row r="32" ht="25" customHeight="1">
       <x:c r="A32" s="1"/>
-      <x:c r="B32" s="22" t="n">
+      <x:c r="B32" s="30" t="n">
         <x:v>0.08</x:v>
       </x:c>
-      <x:c r="C32" s="30"/>
-      <x:c r="D32" s="30"/>
-      <x:c r="E32" s="30"/>
+      <x:c r="C32" s="38"/>
+      <x:c r="D32" s="38"/>
+      <x:c r="E32" s="38"/>
       <x:c r="F32" s="1"/>
       <x:c r="G32" s="1"/>
     </x:row>
@@ -2898,7 +2909,7 @@
     <x:row r="35" ht="25" customHeight="1">
       <x:c r="A35" s="1"/>
       <x:c r="B35" s="6" t="str">
-        <x:v>Slide 23 | Match the stated model</x:v>
+        <x:v>Canva page 31 | Match the stated model</x:v>
       </x:c>
       <x:c r="C35" s="6"/>
       <x:c r="D35" s="6"/>
@@ -2950,7 +2961,7 @@
       <x:c r="B39" s="1" t="str">
         <x:v>Simple present value</x:v>
       </x:c>
-      <x:c r="C39" s="28"/>
+      <x:c r="C39" s="34"/>
       <x:c r="D39" s="1"/>
       <x:c r="E39" s="1"/>
       <x:c r="F39" s="1"/>
@@ -2961,7 +2972,7 @@
       <x:c r="B40" s="1" t="str">
         <x:v>Compound present value</x:v>
       </x:c>
-      <x:c r="C40" s="28"/>
+      <x:c r="C40" s="34"/>
       <x:c r="D40" s="1"/>
       <x:c r="E40" s="1"/>
       <x:c r="F40" s="1"/>
@@ -3244,7 +3255,7 @@
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1"/>
       <x:c r="B3" s="4" t="str">
-        <x:v>Slides 21–24 • Value every payment today using 6% annual compound discounting.</x:v>
+        <x:v>Canva pages 33–35 • Value every payment today using 6% annual compound discounting.</x:v>
       </x:c>
       <x:c r="C3" s="4"/>
       <x:c r="D3" s="4"/>
@@ -3347,7 +3358,7 @@
         <x:v>18000</x:v>
       </x:c>
       <x:c r="D12" s="1"/>
-      <x:c r="E12" s="28"/>
+      <x:c r="E12" s="34"/>
       <x:c r="F12" s="1"/>
       <x:c r="G12" s="1"/>
     </x:row>
@@ -3360,7 +3371,7 @@
         <x:v>22000</x:v>
       </x:c>
       <x:c r="D13" s="1"/>
-      <x:c r="E13" s="28"/>
+      <x:c r="E13" s="34"/>
       <x:c r="F13" s="1"/>
       <x:c r="G13" s="1"/>
     </x:row>
@@ -3373,7 +3384,7 @@
         <x:v>25000</x:v>
       </x:c>
       <x:c r="D14" s="1"/>
-      <x:c r="E14" s="28"/>
+      <x:c r="E14" s="34"/>
       <x:c r="F14" s="1"/>
       <x:c r="G14" s="1"/>
     </x:row>
@@ -3386,7 +3397,7 @@
         <x:v>20000</x:v>
       </x:c>
       <x:c r="D15" s="1"/>
-      <x:c r="E15" s="28"/>
+      <x:c r="E15" s="34"/>
       <x:c r="F15" s="1"/>
       <x:c r="G15" s="1"/>
     </x:row>
@@ -3399,7 +3410,7 @@
         <x:v>15000</x:v>
       </x:c>
       <x:c r="D16" s="1"/>
-      <x:c r="E16" s="28"/>
+      <x:c r="E16" s="34"/>
       <x:c r="F16" s="1"/>
       <x:c r="G16" s="1"/>
     </x:row>
@@ -3410,7 +3421,7 @@
       </x:c>
       <x:c r="C17" s="1"/>
       <x:c r="D17" s="1"/>
-      <x:c r="E17" s="28"/>
+      <x:c r="E17" s="34"/>
       <x:c r="F17" s="1"/>
       <x:c r="G17" s="1"/>
     </x:row>
@@ -3421,52 +3432,52 @@
       </x:c>
       <x:c r="C18" s="1"/>
       <x:c r="D18" s="1"/>
-      <x:c r="E18" s="28"/>
+      <x:c r="E18" s="34"/>
       <x:c r="F18" s="1"/>
       <x:c r="G18" s="1"/>
     </x:row>
     <x:row r="19" ht="25" customHeight="1">
       <x:c r="A19" s="1"/>
-      <x:c r="B19" s="31"/>
-      <x:c r="C19" s="25"/>
-      <x:c r="D19" s="25"/>
-      <x:c r="E19" s="25"/>
+      <x:c r="B19" s="37"/>
+      <x:c r="C19" s="29"/>
+      <x:c r="D19" s="29"/>
+      <x:c r="E19" s="29"/>
       <x:c r="F19" s="1"/>
       <x:c r="G19" s="1"/>
     </x:row>
     <x:row r="20" ht="25" customHeight="1">
       <x:c r="A20" s="1"/>
-      <x:c r="B20" s="25"/>
-      <x:c r="C20" s="25"/>
-      <x:c r="D20" s="25"/>
-      <x:c r="E20" s="25"/>
+      <x:c r="B20" s="29"/>
+      <x:c r="C20" s="29"/>
+      <x:c r="D20" s="29"/>
+      <x:c r="E20" s="29"/>
       <x:c r="F20" s="1"/>
       <x:c r="G20" s="1"/>
     </x:row>
     <x:row r="21" ht="25" customHeight="1">
       <x:c r="A21" s="1"/>
-      <x:c r="B21" s="25"/>
-      <x:c r="C21" s="25"/>
-      <x:c r="D21" s="25"/>
-      <x:c r="E21" s="25"/>
+      <x:c r="B21" s="29"/>
+      <x:c r="C21" s="29"/>
+      <x:c r="D21" s="29"/>
+      <x:c r="E21" s="29"/>
       <x:c r="F21" s="1"/>
       <x:c r="G21" s="1"/>
     </x:row>
     <x:row r="22" ht="25" customHeight="1">
       <x:c r="A22" s="1"/>
-      <x:c r="B22" s="25"/>
-      <x:c r="C22" s="25"/>
-      <x:c r="D22" s="25"/>
-      <x:c r="E22" s="25"/>
+      <x:c r="B22" s="29"/>
+      <x:c r="C22" s="29"/>
+      <x:c r="D22" s="29"/>
+      <x:c r="E22" s="29"/>
       <x:c r="F22" s="1"/>
       <x:c r="G22" s="1"/>
     </x:row>
     <x:row r="23" ht="25" customHeight="1">
       <x:c r="A23" s="1"/>
-      <x:c r="B23" s="25"/>
-      <x:c r="C23" s="25"/>
-      <x:c r="D23" s="25"/>
-      <x:c r="E23" s="25"/>
+      <x:c r="B23" s="29"/>
+      <x:c r="C23" s="29"/>
+      <x:c r="D23" s="29"/>
+      <x:c r="E23" s="29"/>
       <x:c r="F23" s="1"/>
       <x:c r="G23" s="1"/>
     </x:row>
